--- a/data/trans_bre/IP16B05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Edad-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 0,0</t>
+          <t>-43,76; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 0,0</t>
+          <t>-43,76; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 0,0</t>
+          <t>-28,27; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,7</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 0,0</t>
+          <t>-28,27; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,04</t>
+          <t>0,0; 16,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Edad-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 0,0</t>
+          <t>-53,92; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 0,0</t>
+          <t>-53,92; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 0,0</t>
+          <t>-28,46; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 17,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 0,0</t>
+          <t>-28,46; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,54</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
